--- a/doc/手游大事件日历.xlsx
+++ b/doc/手游大事件日历.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="190">
   <si>
     <t>日期</t>
   </si>
@@ -577,6 +577,12 @@
   </si>
   <si>
     <t>《明日方舟终末地》「再次测试」</t>
+  </si>
+  <si>
+    <t>《绝区零》1.6版本更新</t>
+  </si>
+  <si>
+    <t>《绝区零》纽约游戏奖最佳移动游戏</t>
   </si>
   <si>
     <t>《决胜巅峰》国服公测</t>
@@ -1347,7 +1353,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1414,26 +1420,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -2032,11 +2020,11 @@
   <dimension ref="A1:F136"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="15.6666666666667" style="32" customWidth="1"/>
-    <col min="2" max="2" width="7.225" style="32" customWidth="1"/>
-    <col min="3" max="3" width="51.1083333333333" style="32" customWidth="1"/>
-    <col min="4" max="4" width="41.3833333333333" style="32" customWidth="1"/>
-    <col min="5" max="5" width="56.1083333333333" style="32" customWidth="1"/>
+    <col min="1" max="1" width="15.6666666666667" style="26" customWidth="1"/>
+    <col min="2" max="2" width="7.225" style="26" customWidth="1"/>
+    <col min="3" max="3" width="51.1083333333333" style="26" customWidth="1"/>
+    <col min="4" max="4" width="41.3833333333333" style="26" customWidth="1"/>
+    <col min="5" max="5" width="56.1083333333333" style="26" customWidth="1"/>
     <col min="6" max="6" width="84.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2172,7 +2160,7 @@
       <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="27" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="21"/>
@@ -2184,7 +2172,7 @@
       <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
     </row>
@@ -2324,7 +2312,7 @@
       <c r="C22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="27" t="s">
         <v>29</v>
       </c>
       <c r="E22" s="21"/>
@@ -2336,7 +2324,7 @@
       <c r="C23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="34"/>
+      <c r="D23" s="28"/>
       <c r="E23" s="20"/>
       <c r="F23" s="20"/>
     </row>
@@ -2507,7 +2495,7 @@
         <v>43</v>
       </c>
       <c r="D38" s="21"/>
-      <c r="E38" s="33" t="s">
+      <c r="E38" s="27" t="s">
         <v>44</v>
       </c>
       <c r="F38" s="21"/>
@@ -2519,7 +2507,7 @@
         <v>45</v>
       </c>
       <c r="D39" s="15"/>
-      <c r="E39" s="35"/>
+      <c r="E39" s="29"/>
       <c r="F39" s="15"/>
     </row>
     <row r="40" spans="1:6">
@@ -2529,7 +2517,7 @@
         <v>46</v>
       </c>
       <c r="D40" s="15"/>
-      <c r="E40" s="35"/>
+      <c r="E40" s="29"/>
       <c r="F40" s="15"/>
     </row>
     <row r="41" spans="1:6">
@@ -2539,7 +2527,7 @@
         <v>47</v>
       </c>
       <c r="D41" s="15"/>
-      <c r="E41" s="35"/>
+      <c r="E41" s="29"/>
       <c r="F41" s="15"/>
     </row>
     <row r="42" spans="1:6">
@@ -2549,7 +2537,7 @@
         <v>48</v>
       </c>
       <c r="D42" s="15"/>
-      <c r="E42" s="35"/>
+      <c r="E42" s="29"/>
       <c r="F42" s="15"/>
     </row>
     <row r="43" spans="1:6">
@@ -2562,9 +2550,9 @@
       <c r="C43" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D43" s="33"/>
+      <c r="D43" s="27"/>
       <c r="E43" s="21"/>
-      <c r="F43" s="36" t="s">
+      <c r="F43" s="30" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2574,9 +2562,9 @@
       <c r="C44" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D44" s="35"/>
+      <c r="D44" s="29"/>
       <c r="E44" s="15"/>
-      <c r="F44" s="37"/>
+      <c r="F44" s="31"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="17"/>
@@ -2584,9 +2572,9 @@
       <c r="C45" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="35"/>
+      <c r="D45" s="29"/>
       <c r="E45" s="15"/>
-      <c r="F45" s="37"/>
+      <c r="F45" s="31"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="17"/>
@@ -2594,9 +2582,9 @@
       <c r="C46" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D46" s="35"/>
+      <c r="D46" s="29"/>
       <c r="E46" s="15"/>
-      <c r="F46" s="37"/>
+      <c r="F46" s="31"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="10">
@@ -2633,11 +2621,11 @@
       <c r="B49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="33" t="s">
+      <c r="C49" s="27" t="s">
         <v>56</v>
       </c>
       <c r="D49" s="21"/>
-      <c r="E49" s="33" t="s">
+      <c r="E49" s="27" t="s">
         <v>57</v>
       </c>
       <c r="F49" s="4" t="s">
@@ -2647,9 +2635,9 @@
     <row r="50" spans="1:6">
       <c r="A50" s="17"/>
       <c r="B50" s="9"/>
-      <c r="C50" s="35"/>
+      <c r="C50" s="29"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="35"/>
+      <c r="E50" s="29"/>
       <c r="F50" s="4" t="s">
         <v>59</v>
       </c>
@@ -2664,7 +2652,7 @@
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
-      <c r="F51" s="38"/>
+      <c r="F51" s="32"/>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="10">
@@ -2758,24 +2746,24 @@
       <c r="A58" s="17"/>
       <c r="B58" s="9"/>
       <c r="C58" s="15"/>
-      <c r="D58" s="39" t="s">
+      <c r="D58" s="33" t="s">
         <v>68</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="15"/>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="40">
+      <c r="A59" s="34">
         <v>45629</v>
       </c>
-      <c r="B59" s="41" t="s">
+      <c r="B59" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="42"/>
-      <c r="E59" s="36" t="s">
+      <c r="D59" s="36"/>
+      <c r="E59" s="30" t="s">
         <v>70</v>
       </c>
       <c r="F59" s="4" t="s">
@@ -2783,90 +2771,90 @@
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="43"/>
-      <c r="B60" s="44"/>
+      <c r="A60" s="37"/>
+      <c r="B60" s="38"/>
       <c r="C60" s="14"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="37"/>
+      <c r="D60" s="39"/>
+      <c r="E60" s="31"/>
       <c r="F60" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="43"/>
-      <c r="B61" s="44"/>
+      <c r="A61" s="37"/>
+      <c r="B61" s="38"/>
       <c r="C61" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D61" s="45"/>
-      <c r="E61" s="37"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="31"/>
       <c r="F61" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="43"/>
-      <c r="B62" s="44"/>
+      <c r="A62" s="37"/>
+      <c r="B62" s="38"/>
       <c r="C62" s="14"/>
-      <c r="D62" s="45"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="39" t="s">
+      <c r="D62" s="39"/>
+      <c r="E62" s="31"/>
+      <c r="F62" s="33" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="43"/>
-      <c r="B63" s="44"/>
+      <c r="A63" s="37"/>
+      <c r="B63" s="38"/>
       <c r="C63" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="45"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="39" t="s">
+      <c r="D63" s="39"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="33" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="43"/>
-      <c r="B64" s="44"/>
+      <c r="A64" s="37"/>
+      <c r="B64" s="38"/>
       <c r="C64" s="14"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="39" t="s">
+      <c r="D64" s="39"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="33" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="43"/>
-      <c r="B65" s="44"/>
+      <c r="A65" s="37"/>
+      <c r="B65" s="38"/>
       <c r="C65" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="45"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="39" t="s">
+      <c r="D65" s="39"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="33" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="43"/>
-      <c r="B66" s="44"/>
+      <c r="A66" s="37"/>
+      <c r="B66" s="38"/>
       <c r="C66" s="14"/>
-      <c r="D66" s="45"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="39" t="s">
+      <c r="D66" s="39"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="33" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="43"/>
-      <c r="B67" s="44"/>
-      <c r="C67" s="46" t="s">
+      <c r="A67" s="37"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="D67" s="45"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="39" t="s">
+      <c r="D67" s="39"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="33" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2880,7 +2868,7 @@
       <c r="C68" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D68" s="33" t="s">
+      <c r="D68" s="27" t="s">
         <v>85</v>
       </c>
       <c r="E68" s="21"/>
@@ -2892,7 +2880,7 @@
       <c r="C69" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D69" s="34"/>
+      <c r="D69" s="28"/>
       <c r="E69" s="15"/>
       <c r="F69" s="15"/>
     </row>
@@ -2920,7 +2908,7 @@
       </c>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
-      <c r="F71" s="33" t="s">
+      <c r="F71" s="27" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2932,7 +2920,7 @@
       </c>
       <c r="D72" s="15"/>
       <c r="E72" s="15"/>
-      <c r="F72" s="35"/>
+      <c r="F72" s="29"/>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="17"/>
@@ -2942,7 +2930,7 @@
       </c>
       <c r="D73" s="15"/>
       <c r="E73" s="15"/>
-      <c r="F73" s="35"/>
+      <c r="F73" s="29"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="17"/>
@@ -2952,7 +2940,7 @@
       </c>
       <c r="D74" s="15"/>
       <c r="E74" s="15"/>
-      <c r="F74" s="35"/>
+      <c r="F74" s="29"/>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="17"/>
@@ -2962,7 +2950,7 @@
       </c>
       <c r="D75" s="15"/>
       <c r="E75" s="15"/>
-      <c r="F75" s="35"/>
+      <c r="F75" s="29"/>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="18"/>
@@ -2972,13 +2960,13 @@
       </c>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
-      <c r="F76" s="34"/>
+      <c r="F76" s="28"/>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="13">
         <v>45632</v>
       </c>
-      <c r="B77" s="47" t="s">
+      <c r="B77" s="41" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="14" t="s">
@@ -2994,7 +2982,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="17"/>
-      <c r="B78" s="48"/>
+      <c r="B78" s="42"/>
       <c r="C78" s="14"/>
       <c r="D78" s="7"/>
       <c r="E78" s="12"/>
@@ -3004,7 +2992,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="17"/>
-      <c r="B79" s="48"/>
+      <c r="B79" s="42"/>
       <c r="C79" s="4" t="s">
         <v>100</v>
       </c>
@@ -3016,7 +3004,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="48"/>
+      <c r="B80" s="42"/>
       <c r="C80" s="4" t="s">
         <v>102</v>
       </c>
@@ -3030,7 +3018,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="17"/>
-      <c r="B81" s="48"/>
+      <c r="B81" s="42"/>
       <c r="C81" s="4" t="s">
         <v>105</v>
       </c>
@@ -3042,7 +3030,7 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="18"/>
-      <c r="B82" s="49"/>
+      <c r="B82" s="43"/>
       <c r="C82" s="4" t="s">
         <v>107</v>
       </c>
@@ -3127,10 +3115,10 @@
         <v>113</v>
       </c>
       <c r="D88" s="21"/>
-      <c r="E88" s="33" t="s">
+      <c r="E88" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="F88" s="33" t="s">
+      <c r="F88" s="27" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3141,8 +3129,8 @@
         <v>116</v>
       </c>
       <c r="D89" s="15"/>
-      <c r="E89" s="35"/>
-      <c r="F89" s="35"/>
+      <c r="E89" s="29"/>
+      <c r="F89" s="29"/>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="13">
@@ -3155,7 +3143,7 @@
         <v>117</v>
       </c>
       <c r="D90" s="21"/>
-      <c r="E90" s="36" t="s">
+      <c r="E90" s="30" t="s">
         <v>118</v>
       </c>
       <c r="F90" s="21"/>
@@ -3167,7 +3155,7 @@
         <v>119</v>
       </c>
       <c r="D91" s="15"/>
-      <c r="E91" s="37"/>
+      <c r="E91" s="31"/>
       <c r="F91" s="15"/>
     </row>
     <row r="92" spans="1:6">
@@ -3177,7 +3165,7 @@
         <v>120</v>
       </c>
       <c r="D92" s="15"/>
-      <c r="E92" s="37"/>
+      <c r="E92" s="31"/>
       <c r="F92" s="15"/>
     </row>
     <row r="93" spans="1:6">
@@ -3187,7 +3175,7 @@
         <v>121</v>
       </c>
       <c r="D93" s="15"/>
-      <c r="E93" s="37"/>
+      <c r="E93" s="31"/>
       <c r="F93" s="15"/>
     </row>
     <row r="94" spans="1:6">
@@ -3197,7 +3185,7 @@
         <v>122</v>
       </c>
       <c r="D94" s="20"/>
-      <c r="E94" s="50"/>
+      <c r="E94" s="44"/>
       <c r="F94" s="20"/>
     </row>
     <row r="95" spans="1:6">
@@ -3207,11 +3195,11 @@
       <c r="B95" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C95" s="33" t="s">
+      <c r="C95" s="27" t="s">
         <v>123</v>
       </c>
       <c r="D95" s="21"/>
-      <c r="E95" s="36" t="s">
+      <c r="E95" s="30" t="s">
         <v>124</v>
       </c>
       <c r="F95" s="4" t="s">
@@ -3221,9 +3209,9 @@
     <row r="96" spans="1:6">
       <c r="A96" s="17"/>
       <c r="B96" s="9"/>
-      <c r="C96" s="35"/>
+      <c r="C96" s="29"/>
       <c r="D96" s="15"/>
-      <c r="E96" s="37"/>
+      <c r="E96" s="31"/>
       <c r="F96" s="4" t="s">
         <v>126</v>
       </c>
@@ -3231,9 +3219,9 @@
     <row r="97" spans="1:6">
       <c r="A97" s="18"/>
       <c r="B97" s="19"/>
-      <c r="C97" s="34"/>
+      <c r="C97" s="28"/>
       <c r="D97" s="20"/>
-      <c r="E97" s="50"/>
+      <c r="E97" s="44"/>
       <c r="F97" s="4" t="s">
         <v>127</v>
       </c>
@@ -3329,7 +3317,7 @@
       <c r="B105" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C105" s="51" t="s">
+      <c r="C105" s="45" t="s">
         <v>132</v>
       </c>
       <c r="D105" s="14" t="s">
@@ -3343,7 +3331,7 @@
     <row r="106" spans="1:6">
       <c r="A106" s="17"/>
       <c r="B106" s="9"/>
-      <c r="C106" s="51" t="s">
+      <c r="C106" s="45" t="s">
         <v>135</v>
       </c>
       <c r="D106" s="14"/>
@@ -3353,7 +3341,7 @@
     <row r="107" spans="1:6">
       <c r="A107" s="17"/>
       <c r="B107" s="9"/>
-      <c r="C107" s="51" t="s">
+      <c r="C107" s="45" t="s">
         <v>136</v>
       </c>
       <c r="D107" s="14" t="s">
@@ -3365,7 +3353,7 @@
     <row r="108" spans="1:6">
       <c r="A108" s="17"/>
       <c r="B108" s="9"/>
-      <c r="C108" s="27" t="s">
+      <c r="C108" s="22" t="s">
         <v>138</v>
       </c>
       <c r="D108" s="14"/>
@@ -3375,10 +3363,10 @@
     <row r="109" spans="1:6">
       <c r="A109" s="17"/>
       <c r="B109" s="9"/>
-      <c r="C109" s="27" t="s">
+      <c r="C109" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D109" s="33" t="s">
+      <c r="D109" s="27" t="s">
         <v>140</v>
       </c>
       <c r="E109" s="12"/>
@@ -3387,10 +3375,10 @@
     <row r="110" spans="1:6">
       <c r="A110" s="18"/>
       <c r="B110" s="19"/>
-      <c r="C110" s="51" t="s">
+      <c r="C110" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="D110" s="34"/>
+      <c r="D110" s="28"/>
       <c r="E110" s="12"/>
       <c r="F110" s="20"/>
     </row>
@@ -4237,7 +4225,7 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="F36" s="16"/>
     </row>
     <row r="37" ht="18.75" spans="1:6">
       <c r="A37" s="10">
@@ -4246,34 +4234,38 @@
       <c r="B37" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="4"/>
+      <c r="C37" s="4" t="s">
+        <v>182</v>
+      </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="11"/>
+      <c r="F37" s="16" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="38" ht="18.75" spans="1:6">
-      <c r="A38" s="22">
+      <c r="A38" s="13">
         <v>45680</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
+        <v>184</v>
+      </c>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
     </row>
     <row r="39" ht="18.75" spans="1:6">
-      <c r="A39" s="25"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
     </row>
     <row r="40" ht="18.75" spans="1:6">
       <c r="A40" s="10">
@@ -4283,7 +4275,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -4489,7 +4481,7 @@
         <v>15</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -4599,7 +4591,7 @@
         <v>6</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -4673,7 +4665,7 @@
         <v>17</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -4716,7 +4708,7 @@
       <c r="F75" s="4"/>
     </row>
     <row r="76" ht="18.75" spans="1:6">
-      <c r="A76" s="29">
+      <c r="A76" s="23">
         <v>45717</v>
       </c>
       <c r="B76" s="10" t="s">
@@ -5088,7 +5080,7 @@
       <c r="F106" s="4"/>
     </row>
     <row r="107" ht="18.75" spans="1:6">
-      <c r="A107" s="29">
+      <c r="A107" s="23">
         <v>45748</v>
       </c>
       <c r="B107" s="10" t="s">
@@ -5448,7 +5440,7 @@
       <c r="F136" s="16"/>
     </row>
     <row r="137" ht="18.75" spans="1:6">
-      <c r="A137" s="29">
+      <c r="A137" s="23">
         <v>45778</v>
       </c>
       <c r="B137" s="10" t="s">
@@ -7797,7 +7789,7 @@
       <c r="C332" s="4"/>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
-      <c r="F332" s="30"/>
+      <c r="F332" s="24"/>
     </row>
     <row r="333" ht="18.75" spans="1:6">
       <c r="A333" s="10">
@@ -7821,7 +7813,7 @@
       <c r="C334" s="4"/>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
-      <c r="F334" s="30"/>
+      <c r="F334" s="24"/>
     </row>
     <row r="335" ht="18.75" spans="1:6">
       <c r="A335" s="10">
@@ -7917,7 +7909,7 @@
       <c r="C342" s="4"/>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
-      <c r="F342" s="31"/>
+      <c r="F342" s="25"/>
     </row>
     <row r="343" ht="18.75" spans="1:6">
       <c r="A343" s="10">
@@ -8025,7 +8017,7 @@
       <c r="C351" s="4"/>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
-      <c r="F351" s="31"/>
+      <c r="F351" s="25"/>
     </row>
     <row r="352" ht="18.75" spans="1:6">
       <c r="A352" s="10">
@@ -8145,7 +8137,7 @@
       <c r="C361" s="4"/>
       <c r="D361" s="4"/>
       <c r="E361" s="4"/>
-      <c r="F361" s="31"/>
+      <c r="F361" s="25"/>
     </row>
     <row r="362" ht="18.75" spans="1:6">
       <c r="A362" s="10">
